--- a/data_lake/descensos_temperatura/dt=2026-07-22/excel/PronosticoMunicipal_DescensosTemperatura_72h.xlsx
+++ b/data_lake/descensos_temperatura/dt=2026-07-22/excel/PronosticoMunicipal_DescensosTemperatura_72h.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,17 +488,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-22 19:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-23 07:00</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -506,12 +506,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Cuaspud</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,17 +541,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-22 19:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-23 07:00</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -559,12 +559,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>52356</t>
+          <t>52022</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ipiales</t>
+          <t>Aldana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -594,17 +594,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-22 19:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-23 07:00</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -612,12 +612,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>52224</t>
+          <t>52585</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Cuaspud</t>
+          <t>Pupiales</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -647,17 +647,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-22 19:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-23 07:00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -665,12 +665,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>52022</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Aldana</t>
+          <t>Guachucal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -700,17 +700,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-22 19:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-23 07:00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -718,12 +718,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pupiales</t>
+          <t>Cumbal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -732,11 +732,11 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -753,17 +753,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-22 19:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-23 07:00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -771,12 +771,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>52720</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Guachucal</t>
+          <t>Sapuyes</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -806,17 +806,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-22 19:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-23 07:00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -824,12 +824,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>52838</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Cumbal</t>
+          <t>Túquerres</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -838,11 +838,11 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-22 19:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-23 07:00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -877,12 +877,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>52435</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sapuyes</t>
+          <t>Mallama</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -912,17 +912,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-22 19:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-23 07:00</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -930,17 +930,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>86760</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>El Espino</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Putumayo</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -965,17 +965,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-22 19:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-23 07:00</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -983,17 +983,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>52838</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Túquerres</t>
+          <t>Chiscas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-23 19:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-24 07:00</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>41801</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pasto</t>
+          <t>Teruel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-23 19:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-24 07:00</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1089,17 +1089,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>52435</t>
+          <t>19517</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Mallama</t>
+          <t>Páez</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-23 19:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-24 07:00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1142,17 +1142,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>52110</t>
+          <t>73555</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Buesaco</t>
+          <t>Planadas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1195,17 +1195,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>52699</t>
+          <t>73616</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Rioblanco</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1230,17 +1230,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1248,17 +1248,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>52378</t>
+          <t>50370</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Uribe</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1283,17 +1283,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>41206</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Santa Rosa</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1354,25 +1354,25 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>50223</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>San Sebastián</t>
+          <t>Cubarral</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -1389,17 +1389,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1407,17 +1407,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19397</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>La Vega</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>41668</t>
+          <t>73168</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>San Agustín</t>
+          <t>Chaparral</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1495,17 +1495,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>50318</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Saladoblanco</t>
+          <t>Guamal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1548,17 +1548,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1566,17 +1566,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>41359</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Isnos</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1619,17 +1619,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>41378</t>
+          <t>25053</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>La Argentina</t>
+          <t>Arbeláez</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -1654,17 +1654,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>00000</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Area En Litigio Cauca - Huila</t>
+          <t>Gutiérrez</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1725,17 +1725,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>19760</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sotará</t>
+          <t>Pasca</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1778,17 +1778,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>25845</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Puracé</t>
+          <t>Une</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1831,17 +1831,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>19824</t>
+          <t>25178</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Totoró</t>
+          <t>Chipaque</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1866,17 +1866,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1884,17 +1884,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Inzá</t>
+          <t>Choachí</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>25279</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Silvia</t>
+          <t>Fómeque</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1990,17 +1990,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Teruel</t>
+          <t>La Calera</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2025,17 +2025,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2043,25 +2043,25 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19517</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Páez</t>
+          <t>Bogotá, D.C.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>73555</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Planadas</t>
+          <t>Junín</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>73616</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Rioblanco</t>
+          <t>Guasca</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2184,17 +2184,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2202,17 +2202,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>50370</t>
+          <t>25326</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Uribe</t>
+          <t>Guatavita</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>50400</t>
+          <t>25873</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Lejanías</t>
+          <t>Villapinzón</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2308,17 +2308,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>41206</t>
+          <t>25407</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Lenguazaque</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2343,17 +2343,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2361,17 +2361,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>76111</t>
+          <t>25317</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Guachetá</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -2414,25 +2414,25 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Cubarral</t>
+          <t>Ventaquemada</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -2449,17 +2449,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Tota</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2520,17 +2520,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>73168</t>
+          <t>15047</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Chaparral</t>
+          <t>Aquitania</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -2573,25 +2573,25 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>50318</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Guamal</t>
+          <t>Monguí</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -2608,17 +2608,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -2626,17 +2626,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>76834</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>Sogamoso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -2661,17 +2661,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -2679,17 +2679,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>50006</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Acacías</t>
+          <t>Mongua</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -2714,17 +2714,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2732,25 +2732,25 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Tópaga</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -2767,17 +2767,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>73622</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Roncesvalles</t>
+          <t>Gámeza</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -2820,17 +2820,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Arbeláez</t>
+          <t>Corrales</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2891,25 +2891,25 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>15790</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Gutiérrez</t>
+          <t>Tasco</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -2926,17 +2926,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>63302</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Génova</t>
+          <t>Cerinza</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Quindío</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2979,17 +2979,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2997,17 +2997,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Pasca</t>
+          <t>Santa Rosa De Viterbo</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -3032,17 +3032,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>76736</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Duitama</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -3085,17 +3085,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Une</t>
+          <t>Socha</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -3138,17 +3138,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -3156,17 +3156,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>15087</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Chipaque</t>
+          <t>Belén</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3209,17 +3209,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>25181</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Choachí</t>
+          <t>Socotá</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -3244,17 +3244,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -3262,17 +3262,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>25279</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Fómeque</t>
+          <t>Tutazá</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -3297,17 +3297,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>68264</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>La Calera</t>
+          <t>Encino</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -3350,17 +3350,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -3368,25 +3368,25 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bogotá, D.C.</t>
+          <t>Chita</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3403,17 +3403,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3421,25 +3421,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>85136</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Junín</t>
+          <t>La Salina</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Casanare</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3456,17 +3456,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -3474,17 +3474,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>68217</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Guasca</t>
+          <t>Coromoro</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -3509,17 +3509,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Aquitania</t>
+          <t>El Cocuy</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3541,11 +3541,11 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3562,17 +3562,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Monguí</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3615,17 +3615,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sogamoso</t>
+          <t>Guacamayas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Mongua</t>
+          <t>Panqueba</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3721,17 +3721,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -3739,17 +3739,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>68502</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Tópaga</t>
+          <t>Onzaga</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -3774,17 +3774,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Gámeza</t>
+          <t>El Espino</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3827,17 +3827,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -3845,25 +3845,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>15790</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tasco</t>
+          <t>Tame</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3880,17 +3880,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -3898,17 +3898,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>15757</t>
+          <t>68152</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Socha</t>
+          <t>Carcasí</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -3933,17 +3933,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Socotá</t>
+          <t>Güicán De La Sierra</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3965,11 +3965,11 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3986,17 +3986,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -4004,25 +4004,25 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>85136</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>La Salina</t>
+          <t>Chiscas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Casanare</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -4039,17 +4039,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>81300</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>El Cocuy</t>
+          <t>Fortul</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -4110,17 +4110,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>81794</t>
+          <t>68207</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tame</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Arauca</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J70" t="n">
@@ -4145,17 +4145,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -4163,17 +4163,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>68669</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Güicán De La Sierra</t>
+          <t>San Andrés</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J71" t="n">
@@ -4198,17 +4198,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>47053</t>
+          <t>68162</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Aracataca</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4251,17 +4251,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-21 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-22 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -4269,17 +4269,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>47001</t>
+          <t>68318</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>Guaca</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4304,17 +4304,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-22 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-23 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -4322,25 +4322,25 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>68705</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -4357,17 +4357,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-22 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-23 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -4375,25 +4375,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>52356</t>
+          <t>68820</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Ipiales</t>
+          <t>Tona</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -4410,17 +4410,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-22 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-23 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -4428,17 +4428,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>52224</t>
+          <t>54174</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Cuaspud</t>
+          <t>Chitagá</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Norte de Santander</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4463,17 +4463,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-22 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-23 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>52022</t>
+          <t>54743</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Aldana</t>
+          <t>Silos</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Norte de Santander</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -4516,17 +4516,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-22 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-23 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -4534,17 +4534,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>54480</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Pupiales</t>
+          <t>Mutiscua</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Norte de Santander</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-22 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-23 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -4587,871 +4587,23 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>68867</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Guachucal</t>
+          <t>Vetas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J79" t="n">
         <v>3</v>
       </c>
       <c r="K79" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:00</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2026-07-23 07:00</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>12</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>52227</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Cumbal</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Nariño</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>4</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>VERY HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:00</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>2026-07-23 07:00</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>12</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>52720</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sapuyes</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Nariño</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>3</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:00</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>2026-07-23 07:00</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>12</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>52838</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Túquerres</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Nariño</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>3</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:00</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>2026-07-23 07:00</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>12</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>52435</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Mallama</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Nariño</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>3</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:00</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>2026-07-23 07:00</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>12</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>19760</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sotará</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>3</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:00</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>2026-07-23 07:00</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>12</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>19585</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Puracé</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Cauca</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>3</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:00</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>2026-07-23 07:00</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>12</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>15248</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>El Espino</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>3</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>2026-07-22 19:00</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>2026-07-23 07:00</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>12</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>15180</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Chiscas</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>3</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>2026-07-23 19:00</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>2026-07-24 07:00</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>12</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>52317</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Guachucal</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Nariño</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>2</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2026-07-23 19:00</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>2026-07-24 07:00</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>12</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>52227</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Cumbal</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Nariño</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>2</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2026-07-23 19:00</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>2026-07-24 07:00</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>12</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>15183</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Chita</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>3</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2026-07-23 19:00</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>2026-07-24 07:00</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>12</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>85136</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>La Salina</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Casanare</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>3</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2026-07-23 19:00</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>2026-07-24 07:00</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>12</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>15244</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>El Cocuy</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>3</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2026-07-23 19:00</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>2026-07-24 07:00</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>12</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>81794</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Tame</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Arauca</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>3</v>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2026-07-23 19:00</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>2026-07-24 07:00</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>12</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>15332</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Güicán De La Sierra</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J94" t="n">
-        <v>3</v>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>JornadaNocturna</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Nocturna</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2026-07-23 19:00</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>2026-07-24 07:00</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>12</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>15180</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Chiscas</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Boyacá</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>3</v>
-      </c>
-      <c r="K95" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
